--- a/app/reports/CACI_research.xlsx
+++ b/app/reports/CACI_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-21 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-08-22 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>687.66</v>
+        <v>686.9400000000001</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>647.975</v>
+        <v>647.39</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.04734000205993652</v>
+        <v>0.0473799991607666</v>
       </c>
     </row>
     <row r="6">
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="B35" s="21" t="n">
-        <v>22099539.02542536</v>
+        <v>22099540.96294351</v>
       </c>
     </row>
     <row r="36">
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="B37" s="23" t="n">
-        <v>647.975</v>
+        <v>647.39</v>
       </c>
     </row>
     <row r="38">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="C5" s="31" t="n">
-        <v>14319948800</v>
+        <v>14307021824</v>
       </c>
       <c r="D5" s="32" t="n">
         <v>26.81</v>
       </c>
       <c r="E5" s="32" t="n">
-        <v>16.38</v>
+        <v>16.4</v>
       </c>
       <c r="F5" s="32" t="n">
         <v>2.04</v>
@@ -1544,16 +1544,16 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>15853378560</v>
+        <v>15869188096</v>
       </c>
       <c r="D6" s="34" t="n">
-        <v>39.967392</v>
+        <v>40.007244</v>
       </c>
       <c r="E6" s="34" t="n">
-        <v>20.192</v>
+        <v>20.236</v>
       </c>
       <c r="F6" s="34" t="n">
-        <v>5.044</v>
+        <v>5.055</v>
       </c>
     </row>
     <row r="7">
@@ -1568,14 +1568,14 @@
         </is>
       </c>
       <c r="C7" s="33" t="n">
-        <v>12586095616</v>
+        <v>12505928704</v>
       </c>
       <c r="D7" s="34" t="n"/>
       <c r="E7" s="34" t="n">
-        <v>-11.853</v>
+        <v>-12.11</v>
       </c>
       <c r="F7" s="34" t="n">
-        <v>2226.086</v>
+        <v>2274.186</v>
       </c>
     </row>
     <row r="8">
@@ -1590,16 +1590,16 @@
         </is>
       </c>
       <c r="C8" s="33" t="n">
-        <v>5719964160</v>
+        <v>5692107264</v>
       </c>
       <c r="D8" s="34" t="n">
-        <v>15.044776</v>
+        <v>14.971506</v>
       </c>
       <c r="E8" s="34" t="n">
-        <v>6.466</v>
+        <v>6.711</v>
       </c>
       <c r="F8" s="34" t="n">
-        <v>0.867</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="9">
@@ -1614,16 +1614,16 @@
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>21725018112</v>
+        <v>21780514816</v>
       </c>
       <c r="D9" s="34" t="n">
-        <v>30.594099</v>
+        <v>30.672249</v>
       </c>
       <c r="E9" s="34" t="n">
-        <v>21.704</v>
+        <v>22.124</v>
       </c>
       <c r="F9" s="34" t="n">
-        <v>6.056</v>
+        <v>6.173</v>
       </c>
     </row>
     <row r="10">
@@ -1638,16 +1638,16 @@
         </is>
       </c>
       <c r="C10" s="33" t="n">
-        <v>11822140416</v>
+        <v>11808640000</v>
       </c>
       <c r="D10" s="34" t="n">
-        <v>23.838108</v>
+        <v>23.810888</v>
       </c>
       <c r="E10" s="34" t="n">
-        <v>13.857</v>
+        <v>13.95</v>
       </c>
       <c r="F10" s="34" t="n">
-        <v>4.655</v>
+        <v>4.687</v>
       </c>
     </row>
     <row r="11">
@@ -1662,14 +1662,14 @@
         </is>
       </c>
       <c r="C11" s="33" t="n">
-        <v>14322558976</v>
+        <v>14275871744</v>
       </c>
       <c r="D11" s="34" t="n"/>
       <c r="E11" s="34" t="n">
-        <v>35.933</v>
+        <v>36.674</v>
       </c>
       <c r="F11" s="34" t="n">
-        <v>2.134</v>
+        <v>2.178</v>
       </c>
     </row>
     <row r="12">
@@ -1684,14 +1684,14 @@
         </is>
       </c>
       <c r="C12" s="33" t="n">
-        <v>10623336448</v>
+        <v>10572290048</v>
       </c>
       <c r="D12" s="34" t="n"/>
       <c r="E12" s="34" t="n">
-        <v>1128.201</v>
+        <v>1136.415</v>
       </c>
       <c r="F12" s="34" t="n">
-        <v>9.032999999999999</v>
+        <v>9.099</v>
       </c>
     </row>
     <row r="13">
@@ -1707,10 +1707,10 @@
       </c>
       <c r="C13" s="33" t="n"/>
       <c r="D13" s="34" t="n">
-        <v>17.982784</v>
+        <v>17.918339</v>
       </c>
       <c r="E13" s="34" t="n">
-        <v>10.665</v>
+        <v>10.642</v>
       </c>
       <c r="F13" s="34" t="n">
         <v>0.339</v>

--- a/app/reports/CACI_research.xlsx
+++ b/app/reports/CACI_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-22 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-08-23 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>

--- a/app/reports/CACI_research.xlsx
+++ b/app/reports/CACI_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-23 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-08-25 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.585</v>
+        <v>0.63</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>686.9400000000001</v>
+        <v>704.28</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>647.39</v>
+        <v>614.22</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>0.061</v>
+        <v>0.147</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>0.515</v>
+        <v>0.569</v>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
     </row>
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.647</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.0473799991607666</v>
+        <v>0.0464300012588501</v>
       </c>
     </row>
     <row r="6">
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="B35" s="21" t="n">
-        <v>22099540.96294351</v>
+        <v>22099539.47445541</v>
       </c>
     </row>
     <row r="36">
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="B37" s="23" t="n">
-        <v>647.39</v>
+        <v>614.22</v>
       </c>
     </row>
     <row r="38">
@@ -1520,16 +1520,16 @@
         </is>
       </c>
       <c r="C5" s="31" t="n">
-        <v>14307021824</v>
+        <v>13573979136</v>
       </c>
       <c r="D5" s="32" t="n">
-        <v>26.81</v>
+        <v>25.39</v>
       </c>
       <c r="E5" s="32" t="n">
-        <v>16.4</v>
+        <v>16.2</v>
       </c>
       <c r="F5" s="32" t="n">
-        <v>2.04</v>
+        <v>2.01</v>
       </c>
     </row>
     <row r="6">
@@ -1544,16 +1544,16 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>15869188096</v>
+        <v>15031319552</v>
       </c>
       <c r="D6" s="34" t="n">
-        <v>40.007244</v>
+        <v>37.894928</v>
       </c>
       <c r="E6" s="34" t="n">
-        <v>20.236</v>
+        <v>19.602</v>
       </c>
       <c r="F6" s="34" t="n">
-        <v>5.055</v>
+        <v>4.897</v>
       </c>
     </row>
     <row r="7">
@@ -1568,14 +1568,14 @@
         </is>
       </c>
       <c r="C7" s="33" t="n">
-        <v>12505928704</v>
+        <v>11784433664</v>
       </c>
       <c r="D7" s="34" t="n"/>
       <c r="E7" s="34" t="n">
-        <v>-12.11</v>
+        <v>-10.936</v>
       </c>
       <c r="F7" s="34" t="n">
-        <v>2274.186</v>
+        <v>2053.729</v>
       </c>
     </row>
     <row r="8">
@@ -1590,16 +1590,16 @@
         </is>
       </c>
       <c r="C8" s="33" t="n">
-        <v>5692107264</v>
+        <v>5724091392</v>
       </c>
       <c r="D8" s="34" t="n">
-        <v>14.971506</v>
+        <v>15.055631</v>
       </c>
       <c r="E8" s="34" t="n">
-        <v>6.711</v>
+        <v>6.774</v>
       </c>
       <c r="F8" s="34" t="n">
-        <v>0.9</v>
+        <v>0.909</v>
       </c>
     </row>
     <row r="9">
@@ -1614,16 +1614,16 @@
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>21780514816</v>
+        <v>21546084352</v>
       </c>
       <c r="D9" s="34" t="n">
-        <v>30.672249</v>
+        <v>30.317936</v>
       </c>
       <c r="E9" s="34" t="n">
-        <v>22.124</v>
+        <v>21.781</v>
       </c>
       <c r="F9" s="34" t="n">
-        <v>6.173</v>
+        <v>6.077</v>
       </c>
     </row>
     <row r="10">
@@ -1638,16 +1638,16 @@
         </is>
       </c>
       <c r="C10" s="33" t="n">
-        <v>11808640000</v>
+        <v>12186631168</v>
       </c>
       <c r="D10" s="34" t="n">
-        <v>23.810888</v>
+        <v>24.608322</v>
       </c>
       <c r="E10" s="34" t="n">
-        <v>13.95</v>
+        <v>14.309</v>
       </c>
       <c r="F10" s="34" t="n">
-        <v>4.687</v>
+        <v>4.807</v>
       </c>
     </row>
     <row r="11">
@@ -1662,14 +1662,14 @@
         </is>
       </c>
       <c r="C11" s="33" t="n">
-        <v>14275871744</v>
+        <v>14332933120</v>
       </c>
       <c r="D11" s="34" t="n"/>
       <c r="E11" s="34" t="n">
-        <v>36.674</v>
+        <v>36.056</v>
       </c>
       <c r="F11" s="34" t="n">
-        <v>2.178</v>
+        <v>2.141</v>
       </c>
     </row>
     <row r="12">
@@ -1684,14 +1684,14 @@
         </is>
       </c>
       <c r="C12" s="33" t="n">
-        <v>10572290048</v>
+        <v>10084513792</v>
       </c>
       <c r="D12" s="34" t="n"/>
       <c r="E12" s="34" t="n">
-        <v>1136.415</v>
+        <v>1104.189</v>
       </c>
       <c r="F12" s="34" t="n">
-        <v>9.099</v>
+        <v>8.840999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -1707,13 +1707,13 @@
       </c>
       <c r="C13" s="33" t="n"/>
       <c r="D13" s="34" t="n">
-        <v>17.918339</v>
+        <v>17.902937</v>
       </c>
       <c r="E13" s="34" t="n">
-        <v>10.642</v>
+        <v>10.409</v>
       </c>
       <c r="F13" s="34" t="n">
-        <v>0.339</v>
+        <v>0.331</v>
       </c>
     </row>
     <row r="15">
